--- a/liste.xlsx
+++ b/liste.xlsx
@@ -442,7 +442,11 @@
           <t>Fâtiha Suresi</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -442,11 +442,7 @@
           <t>Fâtiha Suresi</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -442,7 +442,11 @@
           <t>Fâtiha Suresi</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5, 5</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 5</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5, 5, 6, 7</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 5, 6, 7</t>
+          <t>5, 4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 4, 5, 6</t>
+          <t>5, 4</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 4</t>
+          <t>5, 6</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13, 14, 15, 17, 18, 22, 24, 27, 28, 32, 38, 40, 42, 43, 44, 45, 48, 49, 55, 57, 59, 60, 61, 39, 40, 41, 42, 43, 44, 45</t>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 13, 14, 15, 17, 18, 22, 24, 27, 28, 32, 38, 39, 40, 40, 41, 42, 42, 43, 43, 44, 44, 45, 45, 48, 49, 55, 57, 59, 60, 61</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>5, 6, 1, 2, 3, 4</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 6, 1, 2, 3, 4</t>
+          <t>2, 3, 4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2, 3, 4, 5, 6</t>
+          <t>3, 4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3, 4, 5, 6</t>
+          <t>4, 5, 6</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4, 5, 6</t>
+          <t>5, 6</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5, 6</t>
+          <t>5</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6, 7, 8, 9, 10, 11, 12, 13, 14, 16, 17, 18, 19, 21, 22, 23, 26, 27, 28, 31, 32, 37, 41, 42, 45, 54, 60, 64, 67, 68, 81, 85</t>
+          <t>7, 8, 9, 10, 11, 12, 13, 14, 16, 17, 18, 19, 21, 22, 23, 26, 27, 28, 31, 32, 37, 41, 42, 45, 54, 60, 64, 67, 68, 81, 85</t>
         </is>
       </c>
     </row>

--- a/liste.xlsx
+++ b/liste.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7, 8, 9, 10, 11, 12, 13, 14, 16, 17, 18, 19, 21, 22, 23, 26, 27, 28, 31, 32, 37, 41, 42, 45, 54, 60, 64, 67, 68, 81, 85</t>
+          <t>7, 8, 9, 10, 11, 12, 13, 14, 16, 17, 18, 19, 21, 22, 23, 26, 27, 28, 31, 32, 37, 41, 42, 45, 54, 60, 64, 67, 68, 81, 85, 6</t>
         </is>
       </c>
     </row>
